--- a/artifacts/aura-forecast/public/exports/Data_Quality_Report.xlsx
+++ b/artifacts/aura-forecast/public/exports/Data_Quality_Report.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Data_Quality" sheetId="1" r:id="rId1"/>
     <sheet name="Cleaning_Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Analysis_Charts" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -1378,180 +1379,355 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>originalYear</t>
+          <t>trainingStart</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026-02-03 00:00:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>convertedYear</t>
+          <t>trainingEnd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-08-31 23:57:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>trainingStart</t>
+          <t>trainingRows</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:25</t>
+          <t>202965</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trainingEnd</t>
+          <t>holdoutRows</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 23:57:21</t>
+          <t>74021</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trainingRows</t>
+          <t>validationStart</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>202965</t>
+          <t>2026-08-03 00:00:18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>holdoutRows</t>
+          <t>validationEnd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>2026-08-31 23:57:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>validationStart</t>
+          <t>forecastStart</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:18</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>validationEnd</t>
+          <t>target</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 23:57:21</t>
+          <t>refractivity</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>forecastStart</t>
+          <t>modelType</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00:00</t>
+          <t>Chronological multivariate linear regression</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>modelFeatureCount</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>refractivity</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>modelType</t>
+          <t>modelFitRows</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chronological multivariate linear regression</t>
+          <t>78838</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>modelFeatureCount</t>
+          <t>validationMetrics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>modelFitRows</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>78838</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>validationMetrics</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>{'mae': 26.136164, 'rmse': 31.693458, 'r2': -4.695695, 'bias': -23.726993, 'mape': 7.119203, 'n': 58217}</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>dateShiftNote</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>The observation dates were calendar-shifted from 2022 to 2026 for the project's forecasting timeline while preserving the original month, day and time structure.</t>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Analysis item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Observation rows</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>286696</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Missing/sentinel values</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>405634</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Metadata or invalid rows</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Exact duplicate rows</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Duplicate timestamps</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Visual asset</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_missingness.svg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Missing percentage by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_outliers.svg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Flagged outlier counts by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>analytics/hist_temperature.svg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Temperature histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>analytics/hist_pressure.svg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pressure histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>analytics/hist_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Refractivity histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analytics/correlation_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Predictor correlation with refractivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>analytics/daily_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Daily refractivity trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>analytics/monthly_forecast.svg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monthly forecast comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>analytics/validation_metrics.svg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chronological validation scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>analytics/training_holdout_rows.svg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Training, holdout, and validation counts</t>
         </is>
       </c>
     </row>

--- a/artifacts/aura-forecast/public/exports/Data_Quality_Report.xlsx
+++ b/artifacts/aura-forecast/public/exports/Data_Quality_Report.xlsx
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>144748</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'mae': 26.136164, 'rmse': 31.693458, 'r2': -4.695695, 'bias': -23.726993, 'mape': 7.119203, 'n': 58217}</t>
+          <t>{'mae': 3.193933, 'rmse': 3.972661, 'r2': 0.910511, 'bias': 1.037282, 'mape': 0.883242, 'n': 58217}</t>
         </is>
       </c>
     </row>
